--- a/outputs/part_c/summaries/part_c_manual_annotation_validation.xlsx
+++ b/outputs/part_c/summaries/part_c_manual_annotation_validation.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,7 +740,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>review_status_present</t>
+          <t>reviewed_confidence_high</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>All review_status values are present.</t>
+          <t>All reviewed rows have high confidence.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -763,18 +763,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143259_0005</t>
-        </is>
-      </c>
+          <t>annotations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>segment_ids_match</t>
+          <t>review_status_present</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>159 segment IDs validated.</t>
+          <t>All review_status values are present.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -802,7 +798,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143320_0007</t>
+          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143259_0005</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -823,7 +819,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>163 segment IDs validated.</t>
+          <t>159 segment IDs validated.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -836,7 +832,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143328_0008</t>
+          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143320_0007</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -857,7 +853,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>159 segment IDs validated.</t>
+          <t>163 segment IDs validated.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -870,7 +866,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143344_0009</t>
+          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143328_0008</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -891,7 +887,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>151 segment IDs validated.</t>
+          <t>159 segment IDs validated.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -904,7 +900,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143401_0011</t>
+          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143344_0009</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -925,13 +921,47 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>151 segment IDs validated.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20260107_Thermal_HKUST/DCIM/DJI_202601071424_001::DJI_20260107143401_0011</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>segment_ids_match</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>144 segment IDs validated.</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>